--- a/docentes/Ochoa Martínez Mayeli - Estadisticos 20212.xlsx
+++ b/docentes/Ochoa Martínez Mayeli - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="53">
   <si>
     <t>Mat</t>
   </si>
@@ -80,6 +80,102 @@
   </si>
   <si>
     <t>Reprobadas</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>BALDERAS</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>ZUÑIGA</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>NAVARRO</t>
+  </si>
+  <si>
+    <t>GUILLEN</t>
+  </si>
+  <si>
+    <t>VELEZ</t>
+  </si>
+  <si>
+    <t>GROTH</t>
+  </si>
+  <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>SORIANO</t>
+  </si>
+  <si>
+    <t>SIERRA</t>
+  </si>
+  <si>
+    <t>RICO</t>
+  </si>
+  <si>
+    <t>PALOMARES</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>LINARES</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>GASCA</t>
+  </si>
+  <si>
+    <t>EMMANUEL</t>
+  </si>
+  <si>
+    <t>HAZIEL</t>
+  </si>
+  <si>
+    <t>JESUS</t>
+  </si>
+  <si>
+    <t>LUIS ALEJANDRO</t>
+  </si>
+  <si>
+    <t>FRANCISCO EMMANUEL</t>
+  </si>
+  <si>
+    <t>KAROL</t>
+  </si>
+  <si>
+    <t>MARLENE</t>
+  </si>
+  <si>
+    <t>KAREN</t>
+  </si>
+  <si>
+    <t>DENISSE MERARY</t>
+  </si>
+  <si>
+    <t>EDITH</t>
+  </si>
+  <si>
+    <t>ROSARIO DOLORES</t>
+  </si>
+  <si>
+    <t>ARELY</t>
   </si>
 </sst>
 </file>
@@ -506,16 +602,19 @@
         <v>35</v>
       </c>
       <c r="D3">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>77.14</v>
+      </c>
+      <c r="H3">
+        <v>8.1</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -607,16 +706,19 @@
         <v>33</v>
       </c>
       <c r="D7">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>87.88</v>
+      </c>
+      <c r="H7">
+        <v>8.6</v>
       </c>
     </row>
   </sheetData>
@@ -695,7 +797,7 @@
         <v>35</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -787,7 +889,7 @@
         <v>33</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="F7">
         <v>0</v>
@@ -872,16 +974,19 @@
         <v>35</v>
       </c>
       <c r="D3">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>77.14</v>
+      </c>
+      <c r="H3">
+        <v>8.1</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -973,16 +1078,19 @@
         <v>33</v>
       </c>
       <c r="D7">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>87.88</v>
+      </c>
+      <c r="H7">
+        <v>8.6</v>
       </c>
     </row>
   </sheetData>
@@ -992,7 +1100,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1022,6 +1130,282 @@
         <v>20</v>
       </c>
     </row>
+    <row r="2" spans="1:7">
+      <c r="A2">
+        <v>19330051920012</v>
+      </c>
+      <c r="B2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>19330051920011</v>
+      </c>
+      <c r="B3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>19330051920010</v>
+      </c>
+      <c r="B4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D4" t="s">
+        <v>43</v>
+      </c>
+      <c r="E4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>19330051920149</v>
+      </c>
+      <c r="B5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D5" t="s">
+        <v>44</v>
+      </c>
+      <c r="E5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>19330051920155</v>
+      </c>
+      <c r="B6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D6" t="s">
+        <v>45</v>
+      </c>
+      <c r="E6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>19330051920181</v>
+      </c>
+      <c r="B7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" t="s">
+        <v>34</v>
+      </c>
+      <c r="D7" t="s">
+        <v>46</v>
+      </c>
+      <c r="E7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>19330051920183</v>
+      </c>
+      <c r="B8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" t="s">
+        <v>35</v>
+      </c>
+      <c r="D8" t="s">
+        <v>47</v>
+      </c>
+      <c r="E8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>19330051920130</v>
+      </c>
+      <c r="B9" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" t="s">
+        <v>36</v>
+      </c>
+      <c r="D9" t="s">
+        <v>48</v>
+      </c>
+      <c r="E9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" t="s">
+        <v>12</v>
+      </c>
+      <c r="G9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>19330051920133</v>
+      </c>
+      <c r="B10" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" t="s">
+        <v>37</v>
+      </c>
+      <c r="D10" t="s">
+        <v>49</v>
+      </c>
+      <c r="E10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" t="s">
+        <v>12</v>
+      </c>
+      <c r="G10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>19330051920195</v>
+      </c>
+      <c r="B11" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11" t="s">
+        <v>38</v>
+      </c>
+      <c r="D11" t="s">
+        <v>50</v>
+      </c>
+      <c r="E11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" t="s">
+        <v>14</v>
+      </c>
+      <c r="G11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>18330051920351</v>
+      </c>
+      <c r="B12" t="s">
+        <v>28</v>
+      </c>
+      <c r="C12" t="s">
+        <v>39</v>
+      </c>
+      <c r="D12" t="s">
+        <v>51</v>
+      </c>
+      <c r="E12" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" t="s">
+        <v>14</v>
+      </c>
+      <c r="G12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>19330051920194</v>
+      </c>
+      <c r="B13" t="s">
+        <v>29</v>
+      </c>
+      <c r="C13" t="s">
+        <v>40</v>
+      </c>
+      <c r="D13" t="s">
+        <v>52</v>
+      </c>
+      <c r="E13" t="s">
+        <v>8</v>
+      </c>
+      <c r="F13" t="s">
+        <v>14</v>
+      </c>
+      <c r="G13">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docentes/Ochoa Martínez Mayeli - Estadisticos 20212.xlsx
+++ b/docentes/Ochoa Martínez Mayeli - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="69">
   <si>
     <t>Mat</t>
   </si>
@@ -85,36 +85,75 @@
     <t>DE JESUS</t>
   </si>
   <si>
+    <t>VEGA</t>
+  </si>
+  <si>
+    <t>MIXCOAC</t>
+  </si>
+  <si>
+    <t>ZUÑIGA</t>
+  </si>
+  <si>
+    <t>CHORA</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>NAVARRO</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>GUILLEN</t>
+  </si>
+  <si>
     <t>BALDERAS</t>
   </si>
   <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>ZUÑIGA</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>NAVARRO</t>
-  </si>
-  <si>
-    <t>GUILLEN</t>
+    <t>GROTH</t>
   </si>
   <si>
     <t>VELEZ</t>
   </si>
   <si>
-    <t>GROTH</t>
-  </si>
-  <si>
     <t>AGUILAR</t>
   </si>
   <si>
     <t>SORIANO</t>
   </si>
   <si>
+    <t>MENCIAS</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>ANTEMATE</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>LINARES</t>
+  </si>
+  <si>
     <t>SIERRA</t>
   </si>
   <si>
@@ -124,19 +163,7 @@
     <t>PALOMARES</t>
   </si>
   <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>LINARES</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
+    <t>VERA</t>
   </si>
   <si>
     <t>GASCA</t>
@@ -145,12 +172,42 @@
     <t>EMMANUEL</t>
   </si>
   <si>
+    <t>JESUS</t>
+  </si>
+  <si>
+    <t>ALAN EDUARDO</t>
+  </si>
+  <si>
+    <t>ELYDEN JULYSSA</t>
+  </si>
+  <si>
+    <t>MARLENE</t>
+  </si>
+  <si>
+    <t>GABRIEL ALEJANDRO</t>
+  </si>
+  <si>
+    <t>DANIELA JAQUELINE</t>
+  </si>
+  <si>
+    <t>KAREN</t>
+  </si>
+  <si>
+    <t>DENISSE MERARY</t>
+  </si>
+  <si>
+    <t>AXEL MIGUEL</t>
+  </si>
+  <si>
+    <t>JOSE ALONSO</t>
+  </si>
+  <si>
+    <t>EDITH</t>
+  </si>
+  <si>
     <t>HAZIEL</t>
   </si>
   <si>
-    <t>JESUS</t>
-  </si>
-  <si>
     <t>LUIS ALEJANDRO</t>
   </si>
   <si>
@@ -160,22 +217,13 @@
     <t>KAROL</t>
   </si>
   <si>
-    <t>MARLENE</t>
-  </si>
-  <si>
-    <t>KAREN</t>
-  </si>
-  <si>
-    <t>DENISSE MERARY</t>
-  </si>
-  <si>
-    <t>EDITH</t>
+    <t>MARIA FERNANDA</t>
+  </si>
+  <si>
+    <t>ARELY</t>
   </si>
   <si>
     <t>ROSARIO DOLORES</t>
-  </si>
-  <si>
-    <t>ARELY</t>
   </si>
 </sst>
 </file>
@@ -1100,7 +1148,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1138,10 +1186,10 @@
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D2" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1155,16 +1203,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>19330051920011</v>
+        <v>19330051920010</v>
       </c>
       <c r="B3" t="s">
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="D3" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1178,16 +1226,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>19330051920010</v>
+        <v>19330051920039</v>
       </c>
       <c r="B4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="D4" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1201,16 +1249,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>19330051920149</v>
+        <v>19330051920168</v>
       </c>
       <c r="B5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="D5" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1224,16 +1272,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>19330051920155</v>
+        <v>19330051920183</v>
       </c>
       <c r="B6" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D6" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1247,22 +1295,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>19330051920181</v>
+        <v>19330051920227</v>
       </c>
       <c r="B7" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D7" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -1270,22 +1318,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>19330051920183</v>
+        <v>19330051920244</v>
       </c>
       <c r="B8" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C8" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="D8" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G8">
         <v>2</v>
@@ -1296,13 +1344,13 @@
         <v>19330051920130</v>
       </c>
       <c r="B9" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="D9" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1319,13 +1367,13 @@
         <v>19330051920133</v>
       </c>
       <c r="B10" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C10" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D10" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -1339,22 +1387,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>19330051920195</v>
+        <v>19330051920101</v>
       </c>
       <c r="B11" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C11" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D11" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G11">
         <v>2</v>
@@ -1362,22 +1410,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>18330051920351</v>
+        <v>19330051920112</v>
       </c>
       <c r="B12" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C12" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D12" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G12">
         <v>2</v>
@@ -1385,16 +1433,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>19330051920194</v>
+        <v>19330051920195</v>
       </c>
       <c r="B13" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C13" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D13" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -1403,6 +1451,167 @@
         <v>14</v>
       </c>
       <c r="G13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>19330051920011</v>
+      </c>
+      <c r="B14" t="s">
+        <v>21</v>
+      </c>
+      <c r="C14" t="s">
+        <v>35</v>
+      </c>
+      <c r="D14" t="s">
+        <v>62</v>
+      </c>
+      <c r="E14" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" t="s">
+        <v>9</v>
+      </c>
+      <c r="G14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>19330051920149</v>
+      </c>
+      <c r="B15" t="s">
+        <v>32</v>
+      </c>
+      <c r="C15" t="s">
+        <v>45</v>
+      </c>
+      <c r="D15" t="s">
+        <v>63</v>
+      </c>
+      <c r="E15" t="s">
+        <v>8</v>
+      </c>
+      <c r="F15" t="s">
+        <v>10</v>
+      </c>
+      <c r="G15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>19330051920155</v>
+      </c>
+      <c r="B16" t="s">
+        <v>21</v>
+      </c>
+      <c r="C16" t="s">
+        <v>46</v>
+      </c>
+      <c r="D16" t="s">
+        <v>64</v>
+      </c>
+      <c r="E16" t="s">
+        <v>8</v>
+      </c>
+      <c r="F16" t="s">
+        <v>10</v>
+      </c>
+      <c r="G16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17">
+        <v>19330051920181</v>
+      </c>
+      <c r="B17" t="s">
+        <v>26</v>
+      </c>
+      <c r="C17" t="s">
+        <v>47</v>
+      </c>
+      <c r="D17" t="s">
+        <v>65</v>
+      </c>
+      <c r="E17" t="s">
+        <v>8</v>
+      </c>
+      <c r="F17" t="s">
+        <v>10</v>
+      </c>
+      <c r="G17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18">
+        <v>19330051920303</v>
+      </c>
+      <c r="B18" t="s">
+        <v>26</v>
+      </c>
+      <c r="C18" t="s">
+        <v>48</v>
+      </c>
+      <c r="D18" t="s">
+        <v>66</v>
+      </c>
+      <c r="E18" t="s">
+        <v>8</v>
+      </c>
+      <c r="F18" t="s">
+        <v>10</v>
+      </c>
+      <c r="G18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19">
+        <v>19330051920194</v>
+      </c>
+      <c r="B19" t="s">
+        <v>33</v>
+      </c>
+      <c r="C19" t="s">
+        <v>49</v>
+      </c>
+      <c r="D19" t="s">
+        <v>67</v>
+      </c>
+      <c r="E19" t="s">
+        <v>8</v>
+      </c>
+      <c r="F19" t="s">
+        <v>14</v>
+      </c>
+      <c r="G19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20">
+        <v>18330051920351</v>
+      </c>
+      <c r="B20" t="s">
+        <v>34</v>
+      </c>
+      <c r="C20" t="s">
+        <v>29</v>
+      </c>
+      <c r="D20" t="s">
+        <v>68</v>
+      </c>
+      <c r="E20" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" t="s">
+        <v>14</v>
+      </c>
+      <c r="G20">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Ochoa Martínez Mayeli - Estadisticos 20212.xlsx
+++ b/docentes/Ochoa Martínez Mayeli - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="64">
   <si>
     <t>Mat</t>
   </si>
@@ -85,142 +85,127 @@
     <t>DE JESUS</t>
   </si>
   <si>
-    <t>VEGA</t>
-  </si>
-  <si>
     <t>MIXCOAC</t>
   </si>
   <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
     <t>ZUÑIGA</t>
   </si>
   <si>
-    <t>CHORA</t>
-  </si>
-  <si>
     <t>VAZQUEZ</t>
   </si>
   <si>
     <t>JIMENEZ</t>
   </si>
   <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>MIXCOHUA</t>
+  </si>
+  <si>
     <t>NAVARRO</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
+    <t>GROTH</t>
+  </si>
+  <si>
+    <t>GUILLEN</t>
+  </si>
+  <si>
+    <t>VELEZ</t>
+  </si>
+  <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>SORIANO</t>
   </si>
   <si>
     <t>MORALES</t>
   </si>
   <si>
-    <t>GUILLEN</t>
-  </si>
-  <si>
-    <t>BALDERAS</t>
-  </si>
-  <si>
-    <t>GROTH</t>
-  </si>
-  <si>
-    <t>VELEZ</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>SORIANO</t>
-  </si>
-  <si>
-    <t>MENCIAS</t>
-  </si>
-  <si>
     <t>ANTONIO</t>
   </si>
   <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
     <t>ANTEMATE</t>
   </si>
   <si>
-    <t>DE LA CRUZ</t>
+    <t>DEL ANGEL</t>
+  </si>
+  <si>
+    <t>ZEPAHUA</t>
+  </si>
+  <si>
+    <t>RICO</t>
+  </si>
+  <si>
+    <t>PALOMARES</t>
+  </si>
+  <si>
+    <t>VERA</t>
+  </si>
+  <si>
+    <t>GASCA</t>
   </si>
   <si>
     <t>LINARES</t>
   </si>
   <si>
-    <t>SIERRA</t>
-  </si>
-  <si>
-    <t>RICO</t>
-  </si>
-  <si>
-    <t>PALOMARES</t>
-  </si>
-  <si>
-    <t>VERA</t>
-  </si>
-  <si>
-    <t>GASCA</t>
-  </si>
-  <si>
     <t>EMMANUEL</t>
   </si>
   <si>
     <t>JESUS</t>
   </si>
   <si>
-    <t>ALAN EDUARDO</t>
-  </si>
-  <si>
     <t>ELYDEN JULYSSA</t>
   </si>
   <si>
+    <t>ABRIL CITLALLI</t>
+  </si>
+  <si>
     <t>MARLENE</t>
   </si>
   <si>
-    <t>GABRIEL ALEJANDRO</t>
-  </si>
-  <si>
     <t>DANIELA JAQUELINE</t>
   </si>
   <si>
     <t>KAREN</t>
   </si>
   <si>
+    <t>AXEL MIGUEL</t>
+  </si>
+  <si>
+    <t>URIEL</t>
+  </si>
+  <si>
+    <t>ALEXIS</t>
+  </si>
+  <si>
+    <t>HAZIEL</t>
+  </si>
+  <si>
+    <t>FRANCISCO EMMANUEL</t>
+  </si>
+  <si>
+    <t>KAROL</t>
+  </si>
+  <si>
+    <t>MARIA FERNANDA</t>
+  </si>
+  <si>
     <t>DENISSE MERARY</t>
   </si>
   <si>
-    <t>AXEL MIGUEL</t>
-  </si>
-  <si>
-    <t>JOSE ALONSO</t>
+    <t>ARELY</t>
   </si>
   <si>
     <t>EDITH</t>
-  </si>
-  <si>
-    <t>HAZIEL</t>
-  </si>
-  <si>
-    <t>LUIS ALEJANDRO</t>
-  </si>
-  <si>
-    <t>FRANCISCO EMMANUEL</t>
-  </si>
-  <si>
-    <t>KAROL</t>
-  </si>
-  <si>
-    <t>MARIA FERNANDA</t>
-  </si>
-  <si>
-    <t>ARELY</t>
   </si>
   <si>
     <t>ROSARIO DOLORES</t>
@@ -647,22 +632,22 @@
         <v>10</v>
       </c>
       <c r="C3">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G3">
-        <v>77.14</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="H3">
-        <v>8.1</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -714,7 +699,7 @@
         <v>81.81999999999999</v>
       </c>
       <c r="H5">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -839,13 +824,13 @@
         <v>10</v>
       </c>
       <c r="C3">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D3">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E3">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -1019,22 +1004,22 @@
         <v>10</v>
       </c>
       <c r="C3">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G3">
-        <v>77.14</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="H3">
-        <v>8.1</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1086,7 +1071,7 @@
         <v>81.81999999999999</v>
       </c>
       <c r="H5">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1148,7 +1133,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1186,10 +1171,10 @@
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1209,10 +1194,10 @@
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D3" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1226,22 +1211,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>19330051920039</v>
+        <v>19330051920168</v>
       </c>
       <c r="B4" t="s">
         <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="D4" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1249,16 +1234,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>19330051920168</v>
+        <v>19330051920176</v>
       </c>
       <c r="B5" t="s">
         <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="D5" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1278,10 +1263,10 @@
         <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D6" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1295,16 +1280,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>19330051920227</v>
+        <v>19330051920244</v>
       </c>
       <c r="B7" t="s">
         <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="D7" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1318,22 +1303,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>19330051920244</v>
+        <v>19330051920130</v>
       </c>
       <c r="B8" t="s">
         <v>26</v>
       </c>
       <c r="C8" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="D8" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G8">
         <v>2</v>
@@ -1341,22 +1326,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>19330051920130</v>
+        <v>19330051920101</v>
       </c>
       <c r="B9" t="s">
         <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D9" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G9">
         <v>2</v>
@@ -1364,22 +1349,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>19330051920133</v>
+        <v>19330051920103</v>
       </c>
       <c r="B10" t="s">
         <v>28</v>
       </c>
       <c r="C10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D10" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G10">
         <v>2</v>
@@ -1387,22 +1372,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>19330051920101</v>
+        <v>19330051920207</v>
       </c>
       <c r="B11" t="s">
         <v>29</v>
       </c>
       <c r="C11" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D11" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G11">
         <v>2</v>
@@ -1410,68 +1395,68 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>19330051920112</v>
+        <v>19330051920011</v>
       </c>
       <c r="B12" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="C12" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="D12" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G12">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>19330051920195</v>
+        <v>19330051920155</v>
       </c>
       <c r="B13" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="C13" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D13" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G13">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>19330051920011</v>
+        <v>19330051920181</v>
       </c>
       <c r="B14" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C14" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="D14" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G14">
         <v>1</v>
@@ -1479,16 +1464,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>19330051920149</v>
+        <v>19330051920303</v>
       </c>
       <c r="B15" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="C15" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D15" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
@@ -1502,22 +1487,22 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>19330051920155</v>
+        <v>19330051920133</v>
       </c>
       <c r="B16" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="C16" t="s">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="D16" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
       </c>
       <c r="F16" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G16">
         <v>1</v>
@@ -1525,22 +1510,22 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>19330051920181</v>
+        <v>19330051920194</v>
       </c>
       <c r="B17" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="C17" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D17" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
       </c>
       <c r="F17" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G17">
         <v>1</v>
@@ -1548,22 +1533,22 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>19330051920303</v>
+        <v>19330051920195</v>
       </c>
       <c r="B18" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C18" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D18" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
       </c>
       <c r="F18" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G18">
         <v>1</v>
@@ -1571,16 +1556,16 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>19330051920194</v>
+        <v>18330051920351</v>
       </c>
       <c r="B19" t="s">
         <v>33</v>
       </c>
       <c r="C19" t="s">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="D19" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
@@ -1589,29 +1574,6 @@
         <v>14</v>
       </c>
       <c r="G19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>18330051920351</v>
-      </c>
-      <c r="B20" t="s">
-        <v>34</v>
-      </c>
-      <c r="C20" t="s">
-        <v>29</v>
-      </c>
-      <c r="D20" t="s">
-        <v>68</v>
-      </c>
-      <c r="E20" t="s">
-        <v>8</v>
-      </c>
-      <c r="F20" t="s">
-        <v>14</v>
-      </c>
-      <c r="G20">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Ochoa Martínez Mayeli - Estadisticos 20212.xlsx
+++ b/docentes/Ochoa Martínez Mayeli - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="55">
   <si>
     <t>Mat</t>
   </si>
@@ -85,130 +85,103 @@
     <t>DE JESUS</t>
   </si>
   <si>
+    <t>VILLEGAS</t>
+  </si>
+  <si>
     <t>MIXCOAC</t>
   </si>
   <si>
+    <t>ALDUCIN</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>ZUÑIGA</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>MIXCOHUA</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>NAVARRO</t>
+  </si>
+  <si>
+    <t>GROTH</t>
+  </si>
+  <si>
+    <t>SORIANO</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
     <t>SANCHEZ</t>
   </si>
   <si>
-    <t>ZUÑIGA</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>MIXCOHUA</t>
-  </si>
-  <si>
-    <t>NAVARRO</t>
-  </si>
-  <si>
-    <t>GROTH</t>
-  </si>
-  <si>
-    <t>GUILLEN</t>
-  </si>
-  <si>
-    <t>VELEZ</t>
+    <t>ROBLES</t>
+  </si>
+  <si>
+    <t>ANTEMATE</t>
+  </si>
+  <si>
+    <t>ZEPAHUA</t>
   </si>
   <si>
     <t>AGUILAR</t>
   </si>
   <si>
-    <t>SORIANO</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>ANTEMATE</t>
-  </si>
-  <si>
-    <t>DEL ANGEL</t>
-  </si>
-  <si>
-    <t>ZEPAHUA</t>
-  </si>
-  <si>
     <t>RICO</t>
   </si>
   <si>
-    <t>PALOMARES</t>
-  </si>
-  <si>
-    <t>VERA</t>
-  </si>
-  <si>
     <t>GASCA</t>
   </si>
   <si>
-    <t>LINARES</t>
+    <t>JESUS</t>
+  </si>
+  <si>
+    <t>IVAN</t>
+  </si>
+  <si>
+    <t>ELYDEN JULYSSA</t>
+  </si>
+  <si>
+    <t>YATZIRI NAOMI</t>
+  </si>
+  <si>
+    <t>KAREN</t>
+  </si>
+  <si>
+    <t>ARACELY</t>
+  </si>
+  <si>
+    <t>AXEL MIGUEL</t>
+  </si>
+  <si>
+    <t>ALEXIS</t>
   </si>
   <si>
     <t>EMMANUEL</t>
   </si>
   <si>
-    <t>JESUS</t>
-  </si>
-  <si>
-    <t>ELYDEN JULYSSA</t>
-  </si>
-  <si>
-    <t>ABRIL CITLALLI</t>
-  </si>
-  <si>
-    <t>MARLENE</t>
+    <t>FRANCISCO EMMANUEL</t>
   </si>
   <si>
     <t>DANIELA JAQUELINE</t>
   </si>
   <si>
-    <t>KAREN</t>
-  </si>
-  <si>
-    <t>AXEL MIGUEL</t>
-  </si>
-  <si>
-    <t>URIEL</t>
-  </si>
-  <si>
-    <t>ALEXIS</t>
-  </si>
-  <si>
-    <t>HAZIEL</t>
-  </si>
-  <si>
-    <t>FRANCISCO EMMANUEL</t>
-  </si>
-  <si>
-    <t>KAROL</t>
-  </si>
-  <si>
-    <t>MARIA FERNANDA</t>
-  </si>
-  <si>
     <t>DENISSE MERARY</t>
   </si>
   <si>
     <t>ARELY</t>
-  </si>
-  <si>
-    <t>EDITH</t>
-  </si>
-  <si>
-    <t>ROSARIO DOLORES</t>
   </si>
 </sst>
 </file>
@@ -804,16 +777,19 @@
         <v>38</v>
       </c>
       <c r="D2">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>71.05</v>
+      </c>
+      <c r="H2">
+        <v>7.6</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -827,16 +803,19 @@
         <v>34</v>
       </c>
       <c r="D3">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>94.12</v>
+      </c>
+      <c r="H3">
+        <v>8.4</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -850,16 +829,19 @@
         <v>24</v>
       </c>
       <c r="D4">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>83.33</v>
+      </c>
+      <c r="H4">
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -873,16 +855,19 @@
         <v>22</v>
       </c>
       <c r="D5">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>77.27</v>
+      </c>
+      <c r="H5">
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -896,16 +881,19 @@
         <v>31</v>
       </c>
       <c r="D6">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>80.65000000000001</v>
+      </c>
+      <c r="H6">
+        <v>7.4</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -919,16 +907,19 @@
         <v>33</v>
       </c>
       <c r="D7">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>93.94</v>
+      </c>
+      <c r="H7">
+        <v>8.6</v>
       </c>
     </row>
   </sheetData>
@@ -984,16 +975,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G2">
-        <v>68.42</v>
+        <v>71.05</v>
       </c>
       <c r="H2">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1010,16 +1001,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="G3">
-        <v>82.34999999999999</v>
+        <v>94.12</v>
       </c>
       <c r="H3">
-        <v>8.4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1036,16 +1027,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F4">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G4">
-        <v>75</v>
+        <v>83.33</v>
       </c>
       <c r="H4">
-        <v>7</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1062,16 +1053,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F5">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G5">
-        <v>81.81999999999999</v>
+        <v>77.27</v>
       </c>
       <c r="H5">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1088,16 +1079,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F6">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G6">
-        <v>77.42</v>
+        <v>80.65000000000001</v>
       </c>
       <c r="H6">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1114,16 +1105,16 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F7">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G7">
-        <v>87.88</v>
+        <v>93.94</v>
       </c>
       <c r="H7">
-        <v>8.6</v>
+        <v>8.9</v>
       </c>
     </row>
   </sheetData>
@@ -1133,7 +1124,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1165,16 +1156,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>19330051920012</v>
+        <v>19330051920010</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1188,16 +1179,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>19330051920010</v>
+        <v>19330051920040</v>
       </c>
       <c r="B3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D3" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1214,13 +1205,13 @@
         <v>19330051920168</v>
       </c>
       <c r="B4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C4" t="s">
         <v>21</v>
       </c>
       <c r="D4" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1234,22 +1225,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>19330051920176</v>
+        <v>19330051920125</v>
       </c>
       <c r="B5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D5" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1257,22 +1248,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>19330051920183</v>
+        <v>19330051920130</v>
       </c>
       <c r="B6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D6" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1280,22 +1271,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>19330051920244</v>
+        <v>19330051920431</v>
       </c>
       <c r="B7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="D7" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -1303,22 +1294,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>19330051920130</v>
+        <v>19330051920101</v>
       </c>
       <c r="B8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="D8" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G8">
         <v>2</v>
@@ -1326,22 +1317,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>19330051920101</v>
+        <v>19330051920207</v>
       </c>
       <c r="B9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C9" t="s">
         <v>38</v>
       </c>
       <c r="D9" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G9">
         <v>2</v>
@@ -1349,68 +1340,68 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>19330051920103</v>
+        <v>19330051920012</v>
       </c>
       <c r="B10" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="C10" t="s">
         <v>39</v>
       </c>
       <c r="D10" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G10">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>19330051920207</v>
+        <v>19330051920155</v>
       </c>
       <c r="B11" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="C11" t="s">
         <v>40</v>
       </c>
       <c r="D11" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G11">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>19330051920011</v>
+        <v>19330051920244</v>
       </c>
       <c r="B12" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="C12" t="s">
         <v>34</v>
       </c>
       <c r="D12" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G12">
         <v>1</v>
@@ -1418,22 +1409,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>19330051920155</v>
+        <v>19330051920133</v>
       </c>
       <c r="B13" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="C13" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="D13" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G13">
         <v>1</v>
@@ -1441,139 +1432,24 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>19330051920181</v>
+        <v>19330051920194</v>
       </c>
       <c r="B14" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="C14" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D14" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>19330051920303</v>
-      </c>
-      <c r="B15" t="s">
-        <v>25</v>
-      </c>
-      <c r="C15" t="s">
-        <v>43</v>
-      </c>
-      <c r="D15" t="s">
-        <v>59</v>
-      </c>
-      <c r="E15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" t="s">
-        <v>10</v>
-      </c>
-      <c r="G15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>19330051920133</v>
-      </c>
-      <c r="B16" t="s">
-        <v>30</v>
-      </c>
-      <c r="C16" t="s">
-        <v>28</v>
-      </c>
-      <c r="D16" t="s">
-        <v>60</v>
-      </c>
-      <c r="E16" t="s">
-        <v>8</v>
-      </c>
-      <c r="F16" t="s">
-        <v>12</v>
-      </c>
-      <c r="G16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>19330051920194</v>
-      </c>
-      <c r="B17" t="s">
-        <v>31</v>
-      </c>
-      <c r="C17" t="s">
-        <v>44</v>
-      </c>
-      <c r="D17" t="s">
-        <v>61</v>
-      </c>
-      <c r="E17" t="s">
-        <v>8</v>
-      </c>
-      <c r="F17" t="s">
-        <v>14</v>
-      </c>
-      <c r="G17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>19330051920195</v>
-      </c>
-      <c r="B18" t="s">
-        <v>32</v>
-      </c>
-      <c r="C18" t="s">
-        <v>45</v>
-      </c>
-      <c r="D18" t="s">
-        <v>62</v>
-      </c>
-      <c r="E18" t="s">
-        <v>8</v>
-      </c>
-      <c r="F18" t="s">
-        <v>14</v>
-      </c>
-      <c r="G18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>18330051920351</v>
-      </c>
-      <c r="B19" t="s">
-        <v>33</v>
-      </c>
-      <c r="C19" t="s">
-        <v>27</v>
-      </c>
-      <c r="D19" t="s">
-        <v>63</v>
-      </c>
-      <c r="E19" t="s">
-        <v>8</v>
-      </c>
-      <c r="F19" t="s">
-        <v>14</v>
-      </c>
-      <c r="G19">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Ochoa Martínez Mayeli - Estadisticos 20212.xlsx
+++ b/docentes/Ochoa Martínez Mayeli - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="24">
   <si>
     <t>Mat</t>
   </si>
@@ -82,106 +82,13 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
     <t>VILLEGAS</t>
   </si>
   <si>
-    <t>MIXCOAC</t>
-  </si>
-  <si>
-    <t>ALDUCIN</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>ZUÑIGA</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>MIXCOHUA</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>NAVARRO</t>
-  </si>
-  <si>
-    <t>GROTH</t>
-  </si>
-  <si>
-    <t>SORIANO</t>
-  </si>
-  <si>
     <t>GARCIA</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>ROBLES</t>
-  </si>
-  <si>
-    <t>ANTEMATE</t>
-  </si>
-  <si>
-    <t>ZEPAHUA</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>RICO</t>
-  </si>
-  <si>
-    <t>GASCA</t>
-  </si>
-  <si>
-    <t>JESUS</t>
-  </si>
-  <si>
     <t>IVAN</t>
-  </si>
-  <si>
-    <t>ELYDEN JULYSSA</t>
-  </si>
-  <si>
-    <t>YATZIRI NAOMI</t>
-  </si>
-  <si>
-    <t>KAREN</t>
-  </si>
-  <si>
-    <t>ARACELY</t>
-  </si>
-  <si>
-    <t>AXEL MIGUEL</t>
-  </si>
-  <si>
-    <t>ALEXIS</t>
-  </si>
-  <si>
-    <t>EMMANUEL</t>
-  </si>
-  <si>
-    <t>FRANCISCO EMMANUEL</t>
-  </si>
-  <si>
-    <t>DANIELA JAQUELINE</t>
-  </si>
-  <si>
-    <t>DENISSE MERARY</t>
-  </si>
-  <si>
-    <t>ARELY</t>
   </si>
 </sst>
 </file>
@@ -975,16 +882,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="F2">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="G2">
-        <v>71.05</v>
+        <v>92.11</v>
       </c>
       <c r="H2">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1001,16 +908,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G3">
-        <v>94.12</v>
+        <v>100</v>
       </c>
       <c r="H3">
-        <v>9</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1027,13 +934,13 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G4">
-        <v>83.33</v>
+        <v>95.83</v>
       </c>
       <c r="H4">
         <v>7.5</v>
@@ -1053,16 +960,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="G5">
-        <v>77.27</v>
+        <v>100</v>
       </c>
       <c r="H5">
-        <v>8.199999999999999</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1079,16 +986,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="G6">
-        <v>80.65000000000001</v>
+        <v>100</v>
       </c>
       <c r="H6">
-        <v>7.6</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1105,16 +1012,16 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F7">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G7">
-        <v>93.94</v>
+        <v>100</v>
       </c>
       <c r="H7">
-        <v>8.9</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1124,7 +1031,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1156,16 +1063,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>19330051920010</v>
+        <v>19330051920040</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="D2" t="s">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1175,282 +1082,6 @@
       </c>
       <c r="G2">
         <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>19330051920040</v>
-      </c>
-      <c r="B3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" t="s">
-        <v>33</v>
-      </c>
-      <c r="D3" t="s">
-        <v>43</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>19330051920168</v>
-      </c>
-      <c r="B4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D4" t="s">
-        <v>44</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>19330051920125</v>
-      </c>
-      <c r="B5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C5" t="s">
-        <v>34</v>
-      </c>
-      <c r="D5" t="s">
-        <v>45</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>19330051920130</v>
-      </c>
-      <c r="B6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C6" t="s">
-        <v>35</v>
-      </c>
-      <c r="D6" t="s">
-        <v>46</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
-        <v>12</v>
-      </c>
-      <c r="G6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>19330051920431</v>
-      </c>
-      <c r="B7" t="s">
-        <v>26</v>
-      </c>
-      <c r="C7" t="s">
-        <v>36</v>
-      </c>
-      <c r="D7" t="s">
-        <v>47</v>
-      </c>
-      <c r="E7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" t="s">
-        <v>12</v>
-      </c>
-      <c r="G7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>19330051920101</v>
-      </c>
-      <c r="B8" t="s">
-        <v>27</v>
-      </c>
-      <c r="C8" t="s">
-        <v>37</v>
-      </c>
-      <c r="D8" t="s">
-        <v>48</v>
-      </c>
-      <c r="E8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" t="s">
-        <v>13</v>
-      </c>
-      <c r="G8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>19330051920207</v>
-      </c>
-      <c r="B9" t="s">
-        <v>28</v>
-      </c>
-      <c r="C9" t="s">
-        <v>38</v>
-      </c>
-      <c r="D9" t="s">
-        <v>49</v>
-      </c>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" t="s">
-        <v>14</v>
-      </c>
-      <c r="G9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>19330051920012</v>
-      </c>
-      <c r="B10" t="s">
-        <v>21</v>
-      </c>
-      <c r="C10" t="s">
-        <v>39</v>
-      </c>
-      <c r="D10" t="s">
-        <v>50</v>
-      </c>
-      <c r="E10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" t="s">
-        <v>9</v>
-      </c>
-      <c r="G10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>19330051920155</v>
-      </c>
-      <c r="B11" t="s">
-        <v>21</v>
-      </c>
-      <c r="C11" t="s">
-        <v>40</v>
-      </c>
-      <c r="D11" t="s">
-        <v>51</v>
-      </c>
-      <c r="E11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" t="s">
-        <v>10</v>
-      </c>
-      <c r="G11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>19330051920244</v>
-      </c>
-      <c r="B12" t="s">
-        <v>29</v>
-      </c>
-      <c r="C12" t="s">
-        <v>34</v>
-      </c>
-      <c r="D12" t="s">
-        <v>52</v>
-      </c>
-      <c r="E12" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" t="s">
-        <v>11</v>
-      </c>
-      <c r="G12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>19330051920133</v>
-      </c>
-      <c r="B13" t="s">
-        <v>30</v>
-      </c>
-      <c r="C13" t="s">
-        <v>34</v>
-      </c>
-      <c r="D13" t="s">
-        <v>53</v>
-      </c>
-      <c r="E13" t="s">
-        <v>8</v>
-      </c>
-      <c r="F13" t="s">
-        <v>12</v>
-      </c>
-      <c r="G13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>19330051920194</v>
-      </c>
-      <c r="B14" t="s">
-        <v>31</v>
-      </c>
-      <c r="C14" t="s">
-        <v>41</v>
-      </c>
-      <c r="D14" t="s">
-        <v>54</v>
-      </c>
-      <c r="E14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" t="s">
-        <v>14</v>
-      </c>
-      <c r="G14">
-        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Ochoa Martínez Mayeli - Estadisticos 20212.xlsx
+++ b/docentes/Ochoa Martínez Mayeli - Estadisticos 20212.xlsx
@@ -82,13 +82,13 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>VILLEGAS</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>IVAN</t>
+    <t>VALDERRAMA</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>EMILIO</t>
   </si>
 </sst>
 </file>
@@ -1063,7 +1063,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>19330051920040</v>
+        <v>19330051920036</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
